--- a/data/trans_dic/Viv_Temp_insuf-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Hogares con temperatura insuficiente (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,69; 64,16</t>
+          <t>31,86; 63,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,47; 60,8</t>
+          <t>38,82; 61,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,81; 58,29</t>
+          <t>38,48; 59,34</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,85; 44,47</t>
+          <t>30,95; 44,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,33; 43,66</t>
+          <t>34,93; 43,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,65; 43,02</t>
+          <t>35,15; 42,67</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,82; 39,76</t>
+          <t>26,57; 39,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,39; 35,71</t>
+          <t>23,83; 36,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,65; 35,77</t>
+          <t>26,54; 35,85</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,95; 42,86</t>
+          <t>32,85; 42,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,15; 41,1</t>
+          <t>34,22; 40,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,35; 40,88</t>
+          <t>35,26; 40,69</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con temperatura insuficiente (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26683</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>30956</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>57639</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17419; 34972</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>24068; 38365</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>44898; 69236</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>183674</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>202524</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>386198</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>142548; 205201</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>180458; 223031</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>343436; 416946</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>49007</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>53772</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>102779</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39272; 58830</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>43474; 66493</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>87639; 118398</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>259364</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>287252</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>546616</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>217794; 282106</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>260441; 311256</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>502176; 579502</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/Viv_Temp_insuf-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,22; 64,08</t>
+          <t>40,77; 63,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,67; 61,08</t>
+          <t>39,03; 64,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,26; 58,16</t>
+          <t>41,88; 59,49</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>41,98%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,48; 44,65</t>
+          <t>36,11; 45,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,16; 43,86</t>
+          <t>39,07; 47,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,94; 42,43</t>
+          <t>38,83; 44,96</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,94; 40,41</t>
+          <t>23,2; 35,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,59; 36,22</t>
+          <t>26,56; 39,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,89; 35,48</t>
+          <t>26,6; 35,74</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,41; 43,03</t>
+          <t>35,49; 42,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,67; 41,28</t>
+          <t>38,31; 44,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,28; 40,8</t>
+          <t>37,75; 42,56</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26683</t>
+          <t>29683</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30956</t>
+          <t>23857</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57639</t>
+          <t>53541</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17069; 35037</t>
+          <t>23132; 36115</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23360; 37870</t>
+          <t>18249; 30328</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45815; 67860</t>
+          <t>43343; 61570</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>270</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>183674</t>
+          <t>194660</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202524</t>
+          <t>186616</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386198</t>
+          <t>381276</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>149583; 205610</t>
+          <t>171781; 216602</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>181632; 226575</t>
+          <t>168952; 204344</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>341452; 414614</t>
+          <t>352589; 408330</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>70</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49007</t>
+          <t>49392</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53772</t>
+          <t>48866</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102779</t>
+          <t>98257</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39822; 59734</t>
+          <t>38856; 59503</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43027; 66072</t>
+          <t>39352; 58818</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>88799; 117165</t>
+          <t>83967; 112806</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>373</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>259364</t>
+          <t>273735</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>287252</t>
+          <t>259338</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>546616</t>
+          <t>533073</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>228107; 285308</t>
+          <t>248371; 297023</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>263853; 314141</t>
+          <t>240325; 280673</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>502386; 580986</t>
+          <t>501050; 564825</t>
         </is>
       </c>
     </row>
